--- a/pipeline/credit_rating/output/fiinratings_xhtn_20261002.xlsx
+++ b/pipeline/credit_rating/output/fiinratings_xhtn_20261002.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O2" s="1" t="n">
@@ -628,7 +628,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O3" s="1" t="n">
@@ -699,7 +699,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O4" s="1" t="n">
@@ -762,7 +762,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O5" s="1" t="n">
@@ -833,7 +833,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O6" s="1" t="n">
@@ -908,7 +908,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O7" s="1" t="n">
@@ -975,7 +975,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O8" s="1" t="n">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O9" s="1" t="n">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O10" s="1" t="n">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O11" s="1" t="n">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O12" s="1" t="n">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O13" s="1" t="n">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O14" s="1" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O15" s="1" t="n">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O16" s="1" t="n">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O17" s="1" t="n">
@@ -1645,7 +1645,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O18" s="1" t="n">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O19" s="1" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O20" s="1" t="n">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O21" s="1" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O22" s="1" t="n">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O23" s="1" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O24" s="1" t="n">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O25" s="1" t="n">
@@ -2177,7 +2177,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O26" s="1" t="n">
@@ -2244,7 +2244,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O27" s="1" t="n">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O28" s="1" t="n">
@@ -2370,7 +2370,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O29" s="1" t="n">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O30" s="1" t="n">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O31" s="1" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O32" s="1" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O33" s="1" t="n">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O34" s="1" t="n">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O35" s="1" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O36" s="1" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O37" s="1" t="n">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O38" s="1" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O39" s="1" t="n">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O40" s="1" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O41" s="1" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O42" s="1" t="n">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O43" s="1" t="n">
@@ -3339,7 +3339,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O44" s="1" t="n">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O45" s="1" t="n">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O46" s="1" t="n">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O47" s="1" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O48" s="1" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O49" s="1" t="n">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O50" s="1" t="n">
@@ -3784,7 +3784,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O51" s="1" t="n">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O52" s="1" t="n">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O53" s="1" t="n">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O54" s="1" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O55" s="1" t="n">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O56" s="1" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O57" s="1" t="n">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O58" s="1" t="n">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O59" s="1" t="n">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O60" s="1" t="n">
@@ -4422,7 +4422,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O61" s="1" t="n">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O62" s="1" t="n">
@@ -4548,7 +4548,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O63" s="1" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O64" s="1" t="n">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O65" s="1" t="n">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O66" s="1" t="n">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O67" s="1" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O68" s="1" t="n">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O69" s="1" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O70" s="1" t="n">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O71" s="1" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O72" s="1" t="n">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O73" s="1" t="n">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O74" s="1" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O75" s="1" t="n">
@@ -5383,7 +5383,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O76" s="1" t="n">
@@ -5446,7 +5446,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O77" s="1" t="n">
@@ -5509,7 +5509,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O78" s="1" t="n">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O79" s="1" t="n">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O80" s="1" t="n">
@@ -5698,7 +5698,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O81" s="1" t="n">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O82" s="1" t="n">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O83" s="1" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O84" s="1" t="n">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O85" s="1" t="n">
@@ -6017,7 +6017,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O86" s="1" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O87" s="1" t="n">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O88" s="1" t="n">
@@ -6206,7 +6206,7 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O89" s="1" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O90" s="1" t="n">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O91" s="1" t="n">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O92" s="1" t="n">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O93" s="1" t="n">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O94" s="1" t="n">
@@ -6584,7 +6584,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O95" s="1" t="n">
@@ -6647,7 +6647,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O96" s="1" t="n">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O97" s="1" t="n">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O98" s="1" t="n">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O99" s="1" t="n">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O100" s="1" t="n">
@@ -6970,7 +6970,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O101" s="1" t="n">
@@ -7033,7 +7033,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O102" s="1" t="n">
@@ -7096,7 +7096,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O103" s="1" t="n">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O104" s="1" t="n">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O105" s="1" t="n">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O106" s="1" t="n">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O107" s="1" t="n">
@@ -7415,7 +7415,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O108" s="1" t="n">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O109" s="1" t="n">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O110" s="1" t="n">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O111" s="1" t="n">
@@ -7671,7 +7671,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O112" s="1" t="n">
@@ -7734,7 +7734,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O113" s="1" t="n">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O114" s="1" t="n">
@@ -7860,7 +7860,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O115" s="1" t="n">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O116" s="1" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O117" s="1" t="n">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O118" s="1" t="n">
@@ -8112,7 +8112,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O119" s="1" t="n">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O120" s="1" t="n">
@@ -8238,7 +8238,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O121" s="1" t="n">
@@ -8301,7 +8301,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O122" s="1" t="n">
@@ -8364,7 +8364,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O123" s="1" t="n">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O124" s="1" t="n">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O125" s="1" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O126" s="1" t="n">
@@ -8616,7 +8616,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O127" s="1" t="n">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O128" s="1" t="n">
@@ -8742,7 +8742,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O129" s="1" t="n">
@@ -8805,7 +8805,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O130" s="1" t="n">
@@ -8872,7 +8872,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O131" s="1" t="n">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O132" s="1" t="n">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O133" s="1" t="n">
@@ -9065,7 +9065,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O134" s="1" t="n">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O135" s="1" t="n">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O136" s="1" t="n">
@@ -9258,7 +9258,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O137" s="1" t="n">
@@ -9321,7 +9321,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O138" s="1" t="n">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O139" s="1" t="n">
@@ -9447,7 +9447,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O140" s="1" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O141" s="1" t="n">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O142" s="1" t="n">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O143" s="1" t="n">
@@ -9699,7 +9699,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O144" s="1" t="n">
@@ -9762,7 +9762,7 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O145" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O146" s="1" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="N147" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O147" s="1" t="n">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O148" s="1" t="n">
@@ -10014,7 +10014,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O149" s="1" t="n">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O150" s="1" t="n">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="N151" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O151" s="1" t="n">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O152" s="1" t="n">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O153" s="1" t="n">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O154" s="1" t="n">
@@ -10392,7 +10392,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O155" s="1" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O156" s="1" t="n">
@@ -10518,7 +10518,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O157" s="1" t="n">
@@ -10581,7 +10581,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O158" s="1" t="n">
@@ -10644,7 +10644,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O159" s="1" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="N160" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O160" s="1" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="N161" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O161" s="1" t="n">
@@ -10833,7 +10833,7 @@
       </c>
       <c r="N162" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O162" s="1" t="n">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N163" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O163" s="1" t="n">
@@ -10959,7 +10959,7 @@
       </c>
       <c r="N164" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O164" s="1" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="N165" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O165" s="1" t="n">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="N166" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O166" s="1" t="n">
@@ -11148,7 +11148,7 @@
       </c>
       <c r="N167" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O167" s="1" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O168" s="1" t="n">
@@ -11274,7 +11274,7 @@
       </c>
       <c r="N169" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O169" s="1" t="n">
@@ -11337,7 +11337,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O170" s="1" t="n">
@@ -11400,7 +11400,7 @@
       </c>
       <c r="N171" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O171" s="1" t="n">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O172" s="1" t="n">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="N173" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O173" s="1" t="n">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="N174" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O174" s="1" t="n">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O175" s="1" t="n">
@@ -11715,7 +11715,7 @@
       </c>
       <c r="N176" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O176" s="1" t="n">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O177" s="1" t="n">
@@ -11841,7 +11841,7 @@
       </c>
       <c r="N178" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O178" s="1" t="n">
@@ -11904,7 +11904,7 @@
       </c>
       <c r="N179" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O179" s="1" t="n">
@@ -11967,7 +11967,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O180" s="1" t="n">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O181" s="1" t="n">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="N182" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O182" s="1" t="n">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="N183" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O183" s="1" t="n">
@@ -12219,7 +12219,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O184" s="1" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="N185" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O185" s="1" t="n">
@@ -12345,7 +12345,7 @@
       </c>
       <c r="N186" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O186" s="1" t="n">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O187" s="1" t="n">
@@ -12471,7 +12471,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O188" s="1" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O189" s="1" t="n">
@@ -12597,7 +12597,7 @@
       </c>
       <c r="N190" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O190" s="1" t="n">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O191" s="1" t="n">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O192" s="1" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="N193" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O193" s="1" t="n">
@@ -12849,7 +12849,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O194" s="1" t="n">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="N195" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O195" s="1" t="n">
@@ -12975,7 +12975,7 @@
       </c>
       <c r="N196" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O196" s="1" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="N197" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O197" s="1" t="n">
@@ -13101,7 +13101,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O198" s="1" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="N199" t="inlineStr">
         <is>
-          <t>2026-10-02 10:00:52</t>
+          <t>2026-10-02 14:55:46</t>
         </is>
       </c>
       <c r="O199" s="1" t="n">
